--- a/Scenarii.xlsx
+++ b/Scenarii.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\msaunier\Desktop\CRIME\8_Modelisation_Foodweb\Europa_foodweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6817B249-9FEE-493D-B776-9A5B8B0FE990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1798B283-BB58-42CE-AC9E-EB31021DE3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8502CAAC-70DA-47CE-A2B3-5C5F3D571F30}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{8502CAAC-70DA-47CE-A2B3-5C5F3D571F30}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario" sheetId="1" r:id="rId1"/>
     <sheet name="Paramètres realistes prédateurs" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
   <si>
     <t>Scenario</t>
   </si>
@@ -133,9 +134,6 @@
     <t>prCoR</t>
   </si>
   <si>
-    <t>10 ou 2 (precisé)</t>
-  </si>
-  <si>
     <t>prCoPBR</t>
   </si>
   <si>
@@ -167,6 +165,30 @@
   </si>
   <si>
     <t>prCHABJ</t>
+  </si>
+  <si>
+    <t>KR</t>
+  </si>
+  <si>
+    <t>100 000</t>
+  </si>
+  <si>
+    <t>Kco</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>0.002</t>
+  </si>
+  <si>
+    <t>0.0001</t>
+  </si>
+  <si>
+    <t>0.1</t>
   </si>
 </sst>
 </file>
@@ -196,7 +218,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -208,21 +230,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -330,9 +337,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -340,51 +356,66 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -755,7 +786,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1337D8E3-E826-4157-A229-696A8DD3D445}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -776,7 +807,7 @@
       <c r="B2" s="5">
         <v>400</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>23</v>
       </c>
     </row>
@@ -787,7 +818,7 @@
       <c r="B3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="13"/>
+      <c r="C3" s="15"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -796,7 +827,7 @@
       <c r="B4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="13"/>
+      <c r="C4" s="15"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
@@ -805,7 +836,7 @@
       <c r="B5" s="7">
         <v>6</v>
       </c>
-      <c r="C5" s="13"/>
+      <c r="C5" s="15"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
@@ -814,7 +845,7 @@
       <c r="B6" s="7">
         <v>1</v>
       </c>
-      <c r="C6" s="13"/>
+      <c r="C6" s="15"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
@@ -823,136 +854,156 @@
       <c r="B7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="13"/>
+      <c r="C7" s="15"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="14"/>
+      <c r="C8" s="15"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="10"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B10" s="12">
         <v>5</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C10" s="13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="5">
+        <v>5000</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-    </row>
+      <c r="C12" s="17"/>
+    </row>
+    <row r="13" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B14">
-        <v>15</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15">
         <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
-      <c r="C18" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B19">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C2:C8"/>
+    <mergeCell ref="C11:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
